--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/FLORIDA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/FLORIDA_2012.xlsx
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C158">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C213">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C245">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C793">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C944">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C945">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1011">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1012">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1020">
@@ -27510,7 +27510,7 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1509">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="B1662" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1662">
